--- a/GameDesign/Excel/Localization/Loc_GachaInfo.xlsx
+++ b/GameDesign/Excel/Localization/Loc_GachaInfo.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,6 +159,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -525,8 +537,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.210625" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -548,22 +560,22 @@
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="22" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>키</t>
         </is>
       </c>
-      <c r="C2" s="22" t="inlineStr">
+      <c r="C2" s="25" t="inlineStr">
         <is>
           <t>한국어(원문)</t>
         </is>
       </c>
-      <c r="D2" s="22" t="inlineStr">
+      <c r="D2" s="25" t="inlineStr">
         <is>
           <t>영어</t>
         </is>
       </c>
-      <c r="E2" s="22" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -575,22 +587,22 @@
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="23" t="n"/>
+      <c r="E3" s="26" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -598,22 +610,22 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E4" s="23" t="n"/>
+      <c r="E4" s="26" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -621,37 +633,37 @@
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
-      <c r="E5" s="23" t="n"/>
+      <c r="E5" s="26" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -674,7 +686,7 @@
           <t>Bead Box</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
+      <c r="E7" s="28" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -693,7 +705,7 @@
           <t>Character Summon</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
+      <c r="E8" s="28" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -712,7 +724,7 @@
           <t>Weapon Draw</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr"/>
+      <c r="E9" s="28" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -731,7 +743,7 @@
           <t>Accessory Draw</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr"/>
+      <c r="E10" s="28" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -750,7 +762,7 @@
           <t>Gem Draw</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr"/>
+      <c r="E11" s="28" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -769,7 +781,7 @@
           <t>Wooden Chest Lv1</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr"/>
+      <c r="E12" s="28" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,7 +800,7 @@
           <t>Silver Chest Lv1</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr"/>
+      <c r="E13" s="28" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -807,7 +819,7 @@
           <t>Golden Chest Lv1</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr"/>
+      <c r="E14" s="28" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -826,7 +838,7 @@
           <t>Wooden Chest Lv2</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
+      <c r="E15" s="28" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
@@ -845,7 +857,7 @@
           <t>Silver Chest Lv2</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr"/>
+      <c r="E16" s="28" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -864,7 +876,7 @@
           <t>Golden Chest Lv2</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr"/>
+      <c r="E17" s="28" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -883,7 +895,7 @@
           <t>Wooden Chest Lv3</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr"/>
+      <c r="E18" s="28" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -902,7 +914,7 @@
           <t>Silver Chest Lv3</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr"/>
+      <c r="E19" s="28" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -921,7 +933,7 @@
           <t>Golden Chest Lv3</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr"/>
+      <c r="E20" s="28" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -940,7 +952,7 @@
           <t>Wooden Chest Lv4</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr"/>
+      <c r="E21" s="28" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
@@ -959,7 +971,7 @@
           <t>Silver Chest Lv4</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr"/>
+      <c r="E22" s="28" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -978,7 +990,7 @@
           <t>Golden Chest Lv4</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr"/>
+      <c r="E23" s="28" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -997,7 +1009,7 @@
           <t>Wooden Chest Lv5</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr"/>
+      <c r="E24" s="28" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1016,7 +1028,7 @@
           <t>Silver Chest Lv5</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr"/>
+      <c r="E25" s="28" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1035,7 +1047,7 @@
           <t>Golden Chest Lv5</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr"/>
+      <c r="E26" s="28" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1054,7 +1066,7 @@
           <t>Secret Vault</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr"/>
+      <c r="E27" s="28" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n"/>
@@ -1073,7 +1085,7 @@
           <t>Appraisal — Muddy Relic</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr"/>
+      <c r="E28" s="28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1092,7 +1104,7 @@
           <t>Appraisal — Shell-Studded Relic</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr"/>
+      <c r="E29" s="28" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1111,7 +1123,7 @@
           <t>Appraisal — Coral-Crusted Relic</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr"/>
+      <c r="E30" s="28" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1130,7 +1142,7 @@
           <t>Appraisal — Sealed Relic</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr"/>
+      <c r="E31" s="28" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1149,7 +1161,7 @@
           <t>Appraisal — Gold-Banded Relic</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr"/>
+      <c r="E32" s="28" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1168,7 +1180,7 @@
           <t>Appraisal — King's Relic</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr"/>
+      <c r="E33" s="28" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
@@ -1187,7 +1199,83 @@
           <t>Appraisal — Rainbow Relic</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr"/>
+      <c r="E34" s="28" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>GachaInfo.32.Name</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>캐릭터 뽑기권 A</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Character Ticket A</t>
+        </is>
+      </c>
+      <c r="E35" s="28" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>GachaInfo.33.Name</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>캐릭터 뽑기권 B</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Character Ticket B</t>
+        </is>
+      </c>
+      <c r="E36" s="28" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>GachaInfo.34.Name</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>캐릭터 뽑기권 C</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Character Ticket C</t>
+        </is>
+      </c>
+      <c r="E37" s="28" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>GachaInfo.35.Name</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>캐릭터 뽑기권 D</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Character Ticket D</t>
+        </is>
+      </c>
+      <c r="E38" s="28" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
